--- a/docs/downloads/13/tbl_repondant_marovoay_tous.xlsx
+++ b/docs/downloads/13/tbl_repondant_marovoay_tous.xlsx
@@ -412,9 +412,6 @@
           <t>Code NA</t>
         </is>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -442,9 +439,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -472,9 +466,6 @@
           <t>Code 10</t>
         </is>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -502,9 +493,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -517,9 +505,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -547,9 +532,6 @@
           <t>Code NA</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -592,9 +574,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,9 +631,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -682,9 +658,6 @@
           <t>Code 10</t>
         </is>
       </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -696,9 +669,6 @@
         <is>
           <t>Code NA</t>
         </is>
-      </c>
-      <c r="C23">
-        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/docs/downloads/13/tbl_repondant_marovoay_tous.xlsx
+++ b/docs/downloads/13/tbl_repondant_marovoay_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -416,7 +416,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -509,7 +509,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -608,7 +608,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
